--- a/1.xlsx
+++ b/1.xlsx
@@ -25,19 +25,22 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
-    <t>Результат1 (0,005 мс., строк: 1)</t>
-  </si>
-  <si>
-    <t>СчетДУ</t>
-  </si>
-  <si>
-    <t>ДатаЗаключения</t>
-  </si>
-  <si>
-    <t>ДатаРасторжения</t>
-  </si>
-  <si>
-    <t>ВидДоговораДоверительногоУправления</t>
+    <t>Результат1 (0,009 мс., строк: 1)</t>
+  </si>
+  <si>
+    <t>Организация</t>
+  </si>
+  <si>
+    <t>СчетДоверительногоУправления</t>
+  </si>
+  <si>
+    <t>Период</t>
+  </si>
+  <si>
+    <t>ВестиЕдиныйБухгалтерскийУчет</t>
+  </si>
+  <si>
+    <t>РЕГИОН ЭсМ</t>
   </si>
   <si>
     <t>Файзутдинов Илдар Шафигуллович</t>
@@ -46,10 +49,7 @@
     <t>18.11.2025 0:00:00</t>
   </si>
   <si>
-    <t>31.12.2028 0:00:00</t>
-  </si>
-  <si>
-    <t>Управление активами физического лица</t>
+    <t>Нет</t>
   </si>
 </sst>
 </file>
@@ -113,7 +113,7 @@
       <b val="false"/>
       <i val="false"/>
       <strike val="false"/>
-      <color rgb="800000"/>
+      <color rgb="2F4F4F"/>
       <sz val="8"/>
       <u val="none"/>
     </font>
@@ -202,13 +202,13 @@
   <sheetFormatPr defaultColWidth="10.5" customHeight="true" defaultRowHeight="11.429"/>
   <cols>
     <col min="1" max="1" width="10.5" style="1" customWidth="true"/>
-    <col min="2" max="2" width="10.5" style="1" customWidth="true"/>
-    <col min="3" max="3" width="10.5" style="1" customWidth="true"/>
-    <col min="4" max="4" width="3.5" style="1" customWidth="true"/>
-    <col min="5" max="5" width="7" style="1" customWidth="true"/>
-    <col min="6" max="6" width="15.16796875" style="1" customWidth="true"/>
+    <col min="2" max="2" width="1.16796875" style="1" customWidth="true"/>
+    <col min="3" max="3" width="9.33203125" style="1" customWidth="true"/>
+    <col min="4" max="4" width="10.5" style="1" customWidth="true"/>
+    <col min="5" max="5" width="10.5" style="1" customWidth="true"/>
+    <col min="6" max="6" width="4.66796875" style="1" customWidth="true"/>
     <col min="7" max="7" width="22.16796875" style="1" customWidth="true"/>
-    <col min="8" max="8" width="65.33203125" style="1" customWidth="true"/>
+    <col min="8" max="8" width="5.83203125" style="1" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1" ht="11" customHeight="true"/>
@@ -222,11 +222,11 @@
         <v>1</v>
       </c>
       <c r="B3" s="3" t="e"/>
-      <c r="C3" s="3" t="e"/>
+      <c r="C3" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="D3" s="3" t="e"/>
-      <c r="E3" s="3" t="s">
-        <v>2</v>
-      </c>
+      <c r="E3" s="3" t="e"/>
       <c r="F3" s="3" t="e"/>
       <c r="G3" s="3" t="s">
         <v>3</v>
@@ -240,12 +240,12 @@
         <v>5</v>
       </c>
       <c r="B4" s="4" t="e"/>
-      <c r="C4" s="4" t="e"/>
+      <c r="C4" s="4" t="s">
+        <v>6</v>
+      </c>
       <c r="D4" s="4" t="e"/>
-      <c r="E4" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" s="5" t="e"/>
+      <c r="E4" s="4" t="e"/>
+      <c r="F4" s="4" t="e"/>
       <c r="G4" s="5" t="s">
         <v>7</v>
       </c>
@@ -255,10 +255,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:F3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:F4"/>
   </mergeCells>
   <pageMargins left="0.393700787401574803149606299" top="0.393700787401574803149606299" right="0.393700787401574803149606299" bottom="0.393700787401574803149606299" header="0" footer="0"/>
   <pageSetup blackAndWhite="false" scale="100" pageOrder="overThenDown" orientation="portrait" paperSize="9"/>
